--- a/US_Area_Codes_GitHub_50_Row_Buyer_Preview.xlsx
+++ b/US_Area_Codes_GitHub_50_Row_Buyer_Preview.xlsx
@@ -1034,12 +1034,14 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22" style="4" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="2" max="2" width="23" style="4" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="16" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22" style="4" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="19" style="4" customWidth="1"/>
+    <col min="9" max="9" width="20.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1">
@@ -1047,10 +1049,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>23</v>
@@ -1075,23 +1077,23 @@
       <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>30</v>
+      <c r="B2" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -1102,23 +1104,23 @@
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>30</v>
+      <c r="B3" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -1129,23 +1131,23 @@
       <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>30</v>
+      <c r="B4" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -1156,23 +1158,23 @@
       <c r="A5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>30</v>
+      <c r="B5" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -1183,23 +1185,23 @@
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>30</v>
+      <c r="B6" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -1210,23 +1212,23 @@
       <c r="A7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>30</v>
+      <c r="B7" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I7" s="3"/>
@@ -1235,23 +1237,23 @@
       <c r="A8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>30</v>
+      <c r="B8" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -1262,23 +1264,23 @@
       <c r="A9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>30</v>
+      <c r="B9" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -1289,23 +1291,23 @@
       <c r="A10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
+      <c r="B10" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -1316,23 +1318,23 @@
       <c r="A11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>30</v>
+      <c r="B11" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -1343,23 +1345,23 @@
       <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
+      <c r="B12" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -1370,23 +1372,23 @@
       <c r="A13" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>30</v>
+      <c r="B13" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -1397,23 +1399,23 @@
       <c r="A14" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>30</v>
+      <c r="B14" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -1424,23 +1426,23 @@
       <c r="A15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
+      <c r="B15" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I15" s="3"/>
@@ -1449,23 +1451,23 @@
       <c r="A16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
+      <c r="B16" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -1476,23 +1478,23 @@
       <c r="A17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>30</v>
+      <c r="B17" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I17" s="3"/>
@@ -1501,23 +1503,23 @@
       <c r="A18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>30</v>
+      <c r="B18" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I18" s="3"/>
@@ -1526,23 +1528,23 @@
       <c r="A19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>30</v>
+      <c r="B19" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="5" t="s">
         <v>84</v>
       </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I19" s="3" t="s">
@@ -1553,23 +1555,23 @@
       <c r="A20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>30</v>
+      <c r="B20" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="5" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -1580,23 +1582,23 @@
       <c r="A21" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>30</v>
+      <c r="B21" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -1607,23 +1609,23 @@
       <c r="A22" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>30</v>
+      <c r="B22" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="5" t="s">
         <v>94</v>
       </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="3"/>
@@ -1632,23 +1634,23 @@
       <c r="A23" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>30</v>
+      <c r="B23" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="5" t="s">
         <v>97</v>
       </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I23" s="3" t="s">
@@ -1659,23 +1661,23 @@
       <c r="A24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>30</v>
+      <c r="B24" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="5" t="s">
         <v>101</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I24" s="3"/>
@@ -1684,23 +1686,23 @@
       <c r="A25" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>30</v>
+      <c r="B25" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="5" t="s">
         <v>104</v>
       </c>
       <c r="G25" s="3"/>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I25" s="3"/>
@@ -1709,23 +1711,23 @@
       <c r="A26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>30</v>
+      <c r="B26" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I26" s="3"/>
@@ -1734,23 +1736,23 @@
       <c r="A27" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>30</v>
+      <c r="B27" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="5" t="s">
         <v>109</v>
       </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -1761,23 +1763,23 @@
       <c r="A28" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>30</v>
+      <c r="B28" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="5" t="s">
         <v>113</v>
       </c>
       <c r="G28" s="3"/>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -1788,23 +1790,23 @@
       <c r="A29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>30</v>
+      <c r="B29" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="5" t="s">
         <v>117</v>
       </c>
       <c r="G29" s="3"/>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I29" s="3"/>
@@ -1813,23 +1815,23 @@
       <c r="A30" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>30</v>
+      <c r="B30" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="5" t="s">
         <v>119</v>
       </c>
       <c r="G30" s="3"/>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -1840,23 +1842,23 @@
       <c r="A31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>30</v>
+      <c r="B31" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="5" t="s">
         <v>121</v>
       </c>
       <c r="G31" s="3"/>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -1867,23 +1869,23 @@
       <c r="A32" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>30</v>
+      <c r="B32" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="5" t="s">
         <v>124</v>
       </c>
       <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I32" s="3"/>
@@ -1892,23 +1894,23 @@
       <c r="A33" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>30</v>
+      <c r="B33" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="5" t="s">
         <v>127</v>
       </c>
       <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I33" s="3"/>
@@ -1917,25 +1919,25 @@
       <c r="A34" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>30</v>
+      <c r="B34" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="5" t="s">
         <v>129</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I34" s="3"/>
@@ -1944,23 +1946,23 @@
       <c r="A35" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>30</v>
+      <c r="B35" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="5" t="s">
         <v>132</v>
       </c>
       <c r="G35" s="3"/>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I35" s="3"/>
@@ -1969,23 +1971,23 @@
       <c r="A36" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>30</v>
+      <c r="B36" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="5" t="s">
         <v>134</v>
       </c>
       <c r="G36" s="3"/>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I36" s="3" t="s">
@@ -1996,23 +1998,23 @@
       <c r="A37" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>30</v>
+      <c r="B37" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="5" t="s">
         <v>137</v>
       </c>
       <c r="G37" s="3"/>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I37" s="3"/>
@@ -2021,23 +2023,23 @@
       <c r="A38" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>30</v>
+      <c r="B38" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="5" t="s">
         <v>140</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I38" s="3"/>
@@ -2046,23 +2048,23 @@
       <c r="A39" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>30</v>
+      <c r="B39" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="5" t="s">
         <v>142</v>
       </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="3" t="s">
@@ -2073,23 +2075,23 @@
       <c r="A40" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>30</v>
+      <c r="B40" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="5" t="s">
         <v>144</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I40" s="3"/>
@@ -2098,23 +2100,23 @@
       <c r="A41" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>30</v>
+      <c r="B41" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="5" t="s">
         <v>147</v>
       </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I41" s="3" t="s">
@@ -2125,23 +2127,23 @@
       <c r="A42" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>30</v>
+      <c r="B42" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="5" t="s">
         <v>150</v>
       </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -2152,23 +2154,23 @@
       <c r="A43" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>30</v>
+      <c r="B43" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -2179,23 +2181,23 @@
       <c r="A44" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>30</v>
+      <c r="B44" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="5" t="s">
         <v>157</v>
       </c>
       <c r="G44" s="3"/>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I44" s="3"/>
@@ -2204,23 +2206,23 @@
       <c r="A45" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>30</v>
+      <c r="B45" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="5" t="s">
         <v>159</v>
       </c>
       <c r="G45" s="3"/>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I45" s="3" t="s">
@@ -2231,23 +2233,23 @@
       <c r="A46" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>30</v>
+      <c r="B46" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="5" t="s">
         <v>162</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I46" s="3" t="s">
@@ -2258,23 +2260,23 @@
       <c r="A47" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>30</v>
+      <c r="B47" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="5" t="s">
         <v>165</v>
       </c>
       <c r="G47" s="3"/>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I47" s="3" t="s">
@@ -2285,23 +2287,23 @@
       <c r="A48" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>30</v>
+      <c r="B48" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G48" s="3"/>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -2312,23 +2314,23 @@
       <c r="A49" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>30</v>
+      <c r="B49" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="3"/>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I49" s="3"/>
@@ -2337,23 +2339,23 @@
       <c r="A50" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>30</v>
+      <c r="B50" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G50" s="3"/>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I50" s="3" t="s">
@@ -2364,23 +2366,23 @@
       <c r="A51" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>30</v>
+      <c r="B51" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G51" s="3"/>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I51" s="3" t="s">
@@ -2389,13 +2391,13 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
+      <c r="B52" s="6"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="6"/>
       <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="F52" s="6"/>
       <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+      <c r="H52" s="6"/>
       <c r="I52" s="7"/>
     </row>
   </sheetData>
